--- a/Data/Hires/testDataRomania.xlsx
+++ b/Data/Hires/testDataRomania.xlsx
@@ -1,34 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F43526-FC81-49E9-BD65-07364E0A05DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="213">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -264,7 +250,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10651303</t>
+    <t>10652060</t>
   </si>
   <si>
     <t>Passed</t>
@@ -276,10 +262,10 @@
     <t>Romania</t>
   </si>
   <si>
-    <t>Jermey</t>
-  </si>
-  <si>
-    <t>Shanahan</t>
+    <t>Ebba</t>
+  </si>
+  <si>
+    <t>Treutel</t>
   </si>
   <si>
     <t>Mobile</t>
@@ -369,6 +355,9 @@
     <t>Personal Numeric Code (CNP)</t>
   </si>
   <si>
+    <t>5001101328667</t>
+  </si>
+  <si>
     <t>01/01/2000</t>
   </si>
   <si>
@@ -420,13 +409,13 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10651305</t>
-  </si>
-  <si>
-    <t>Florencio</t>
-  </si>
-  <si>
-    <t>Hahn-Maggio</t>
+    <t>10652061</t>
+  </si>
+  <si>
+    <t>Breanne</t>
+  </si>
+  <si>
+    <t>Heaney</t>
   </si>
   <si>
     <t>Fixed Term (Fixed Term)</t>
@@ -441,25 +430,25 @@
     <t>Test3</t>
   </si>
   <si>
-    <t>10651306</t>
+    <t>10652062</t>
   </si>
   <si>
     <t>880 Store Management (Dewes Kiwoba (10629083))</t>
   </si>
   <si>
-    <t>Maritza</t>
-  </si>
-  <si>
-    <t>Schinner</t>
-  </si>
-  <si>
-    <t>Auto 7404823</t>
+    <t>Madyson</t>
+  </si>
+  <si>
+    <t>Jaskolski</t>
+  </si>
+  <si>
+    <t>Auto 37414694</t>
   </si>
   <si>
     <t>Store Manager_NEW</t>
   </si>
   <si>
-    <t>92 Retail Management </t>
+    <t xml:space="preserve">92 Retail Management </t>
   </si>
   <si>
     <t>251 Management Retail</t>
@@ -468,16 +457,16 @@
     <t>Test4</t>
   </si>
   <si>
-    <t>10651309</t>
-  </si>
-  <si>
-    <t>Zella</t>
-  </si>
-  <si>
-    <t>Rosenbaum</t>
-  </si>
-  <si>
-    <t>Auto 37778177</t>
+    <t>10652063</t>
+  </si>
+  <si>
+    <t>Maye</t>
+  </si>
+  <si>
+    <t>Kilback</t>
+  </si>
+  <si>
+    <t>Auto 81961432</t>
   </si>
   <si>
     <t>In-Store P&amp;C Manager_NEW</t>
@@ -486,16 +475,22 @@
     <t>Test5</t>
   </si>
   <si>
-    <t>10651310</t>
-  </si>
-  <si>
-    <t>Elijah</t>
-  </si>
-  <si>
-    <t>Beatty</t>
-  </si>
-  <si>
-    <t>Auto 96406514</t>
+    <t xml:space="preserve">Test failed for 'Rey Schmeler' Employee:{}TimeoutError: locator.fill: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('text=Email AddressEmail AddressTypeType0 items selectedPrimary WorkPrimary WorkPrimar').locator('input[role="textbox"]')[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Rey</t>
+  </si>
+  <si>
+    <t>Schmeler</t>
+  </si>
+  <si>
+    <t>Auto 59617664</t>
   </si>
   <si>
     <t>Assistant Store Manager_NEW</t>
@@ -504,16 +499,16 @@
     <t>Test6</t>
   </si>
   <si>
-    <t>10651313</t>
-  </si>
-  <si>
-    <t>Bertram</t>
-  </si>
-  <si>
-    <t>Cummerata</t>
-  </si>
-  <si>
-    <t>Auto 81490807</t>
+    <t>10652064</t>
+  </si>
+  <si>
+    <t>Hermina</t>
+  </si>
+  <si>
+    <t>Jones</t>
+  </si>
+  <si>
+    <t>Auto 1715116</t>
   </si>
   <si>
     <t>Department Manager_NEW</t>
@@ -522,16 +517,16 @@
     <t>Test7</t>
   </si>
   <si>
-    <t>10651314</t>
-  </si>
-  <si>
-    <t>Onie</t>
-  </si>
-  <si>
-    <t>Kuhn</t>
-  </si>
-  <si>
-    <t>Auto 29057449</t>
+    <t>10652065</t>
+  </si>
+  <si>
+    <t>Nash</t>
+  </si>
+  <si>
+    <t>Walsh</t>
+  </si>
+  <si>
+    <t>Auto 37093065</t>
   </si>
   <si>
     <t>Team Manager - Retail_NEW</t>
@@ -540,16 +535,16 @@
     <t>Test8</t>
   </si>
   <si>
-    <t>10651316</t>
-  </si>
-  <si>
-    <t>Letha</t>
-  </si>
-  <si>
-    <t>Zboncak</t>
-  </si>
-  <si>
-    <t>Auto 9670109</t>
+    <t>10652066</t>
+  </si>
+  <si>
+    <t>Brian</t>
+  </si>
+  <si>
+    <t>Blanda</t>
+  </si>
+  <si>
+    <t>Auto 15412552</t>
   </si>
   <si>
     <t>Visual Merchandising Manager_NEW</t>
@@ -558,13 +553,13 @@
     <t>Test9</t>
   </si>
   <si>
-    <t>10651328</t>
-  </si>
-  <si>
-    <t>Albertha</t>
-  </si>
-  <si>
-    <t>Greenfelder</t>
+    <t>10652067</t>
+  </si>
+  <si>
+    <t>Jayde</t>
+  </si>
+  <si>
+    <t>Buckridge</t>
   </si>
   <si>
     <t>In-Store P&amp;C Assistant_NEW</t>
@@ -580,16 +575,13 @@
     <t>Test10</t>
   </si>
   <si>
-    <t>Test failed for 'Melvin O'Kon' Employee: undefined&amp; find failed Screenshot Path:-&gt;h:\WorkDaySuite_Playwright/WorkdayFailedScreenshot/2024-10-21T08-28-32-616Z.png</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>Melvin</t>
-  </si>
-  <si>
-    <t>O'Kon</t>
+    <t>10652068</t>
+  </si>
+  <si>
+    <t>Bernadine</t>
+  </si>
+  <si>
+    <t>Casper</t>
   </si>
   <si>
     <t>Visual Merchandiser_NEW</t>
@@ -601,13 +593,13 @@
     <t>Test11</t>
   </si>
   <si>
-    <t>10651326</t>
-  </si>
-  <si>
-    <t>Rahul</t>
-  </si>
-  <si>
-    <t>Runolfsdottir-Armstrong</t>
+    <t>10652069</t>
+  </si>
+  <si>
+    <t>Jamie</t>
+  </si>
+  <si>
+    <t>Borer</t>
   </si>
   <si>
     <t>In-Store P&amp;C Supervisor_NEW</t>
@@ -616,13 +608,13 @@
     <t>Test12</t>
   </si>
   <si>
-    <t>10651329</t>
-  </si>
-  <si>
-    <t>Crawford</t>
-  </si>
-  <si>
-    <t>Kautzer</t>
+    <t>Test failed for 'Carissa O'Keefe' Employee: undefined&amp; find failed Screenshot Path:-&gt;H:\WorkDaySuite_Playwright/WorkdayFailedScreenshot/2024-11-07T09-30-39-352Z.png</t>
+  </si>
+  <si>
+    <t>Carissa</t>
+  </si>
+  <si>
+    <t>O'Keefe</t>
   </si>
   <si>
     <t>05 Children’s Wear</t>
@@ -631,93 +623,93 @@
     <t>Test13</t>
   </si>
   <si>
-    <t>Test failed for 'Amara Franey' Employee: Errors and AlertsErrorsEmployee TypeThe field Employee Type is required and must have a value.Job ProfileThe field Job Profile is required and must have a value.Time TypeThe field Time Type is required and must have a value.LocationThe field Location is required and must have a value.AlertFTEThe FTE is zero. The FTE value can affect FTE reporting, benefits, and payroll for the worker. Ensure that the Default Weekly Hours and Scheduled Weekly Hours are correct. &amp; find failed Screenshot Path:-&gt;h:\WorkDaySuite_Playwright/WorkdayFailedScreenshot/2024-10-21T08-40-40-991Z.png</t>
-  </si>
-  <si>
-    <t>Amara</t>
-  </si>
-  <si>
-    <t>Franey</t>
+    <t>10652070</t>
+  </si>
+  <si>
+    <t>Elvie</t>
+  </si>
+  <si>
+    <t>Goldner</t>
   </si>
   <si>
     <t>Test14</t>
   </si>
   <si>
-    <t>10651319</t>
-  </si>
-  <si>
-    <t>Rita</t>
-  </si>
-  <si>
-    <t>Howe</t>
-  </si>
-  <si>
-    <t>Auto 22497314</t>
+    <t>10652071</t>
+  </si>
+  <si>
+    <t>Peggie</t>
+  </si>
+  <si>
+    <t>Schiller</t>
+  </si>
+  <si>
+    <t>Auto 80408749</t>
   </si>
   <si>
     <t>Test15</t>
   </si>
   <si>
-    <t>10651331</t>
-  </si>
-  <si>
-    <t>Jeffry</t>
-  </si>
-  <si>
-    <t>Gislason</t>
+    <t>10652072</t>
+  </si>
+  <si>
+    <t>Claude</t>
+  </si>
+  <si>
+    <t>Conroy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="4"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="4"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -731,7 +723,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -739,6 +731,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -757,12 +754,8 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -772,34 +765,24 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top style="thin"/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -880,9 +863,6 @@
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -895,6 +875,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -911,6 +894,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1214,9 +1200,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CD32"/>
-  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.81640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.81640625" style="1" customWidth="1"/>
@@ -1302,7 +1288,7 @@
     <col min="83" max="83" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:82" s="3" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.5" customHeight="1" spans="1:82" s="3" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1550,7 +1536,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:82" s="8" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="15.65" customHeight="1" spans="1:82" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>77</v>
       </c>
@@ -1582,8 +1568,8 @@
         <v>85</v>
       </c>
       <c r="K2" s="14">
-        <f ca="1">TODAY()-100</f>
-        <v>45489</v>
+        <f>TODAY()-100</f>
+        <v>45503</v>
       </c>
       <c r="L2" s="11" t="s">
         <v>81</v>
@@ -1619,8 +1605,8 @@
         <v>85</v>
       </c>
       <c r="W2" s="14">
-        <f ca="1">TODAY()-100</f>
-        <v>45489</v>
+        <f>TODAY()-100</f>
+        <v>45503</v>
       </c>
       <c r="X2" s="13" t="s">
         <v>92</v>
@@ -1688,9 +1674,9 @@
       <c r="AS2" s="13">
         <v>1</v>
       </c>
-      <c r="AT2" s="14" t="str">
-        <f t="shared" ref="AT2:AT16" ca="1" si="0">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>16/07/2024</v>
+      <c r="AT2" s="14">
+        <f t="shared" ref="AT2:AT16" si="0">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>NaN</v>
       </c>
       <c r="AU2" s="11" t="s">
         <v>100</v>
@@ -1705,12 +1691,12 @@
         <v>111</v>
       </c>
       <c r="AY2" s="14">
-        <f ca="1">TODAY()-100</f>
-        <v>45489</v>
+        <f>TODAY()-100</f>
+        <v>45503</v>
       </c>
       <c r="AZ2" s="14">
-        <f ca="1">TODAY()-100</f>
-        <v>45489</v>
+        <f>TODAY()-100</f>
+        <v>45503</v>
       </c>
       <c r="BA2" s="23" t="s">
         <v>100</v>
@@ -1721,95 +1707,95 @@
       <c r="BC2" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="BD2" s="28">
-        <v>1930501340702</v>
+      <c r="BD2" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="BE2" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BF2" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG2" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH2" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI2" s="1">
+        <f t="array" ref="BI2:BI16">_xlfn.RANDARRAY(15,1,123456,999999,TRUE)</f>
+        <v>979313</v>
+      </c>
+      <c r="BJ2" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BG2" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH2" s="27" t="s">
+      <c r="BK2" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="BI2" s="1">
-        <f t="array" aca="1" ref="BI2:BI16" ca="1">_xlfn.RANDARRAY(15,1,123456,999999,TRUE)</f>
-        <v>675322</v>
-      </c>
-      <c r="BJ2" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK2" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL2" s="29" t="s">
+      <c r="BL2" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BM2" s="29" t="s">
+      <c r="BM2" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BN2" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="BO2" s="29" t="s">
+      <c r="BN2" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="BP2" s="29" t="s">
+      <c r="BO2" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="BQ2" s="29" t="s">
+      <c r="BP2" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ2" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="BR2" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS2" s="29" t="s">
+      <c r="BR2" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS2" s="28" t="s">
         <v>100</v>
       </c>
       <c r="BT2" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU2" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="BV2" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW2" s="30" t="s">
+      <c r="BV2" s="29" t="s">
         <v>122</v>
       </c>
+      <c r="BW2" s="29" t="s">
+        <v>123</v>
+      </c>
       <c r="BX2" s="26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BY2" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BZ2" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="CA2" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB2" s="26" t="s">
         <v>81</v>
       </c>
       <c r="CC2" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD2" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="15.65" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>79</v>
@@ -1821,10 +1807,10 @@
         <v>81</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H3" s="13">
         <v>720527700</v>
@@ -1836,10 +1822,10 @@
         <v>85</v>
       </c>
       <c r="K3" s="14">
-        <f t="shared" ref="K3:K16" ca="1" si="1">TODAY()-100</f>
-        <v>45489</v>
-      </c>
-      <c r="L3" s="29" t="s">
+        <f t="shared" ref="K3:K16" si="1">TODAY()-100</f>
+        <v>45503</v>
+      </c>
+      <c r="L3" s="28" t="s">
         <v>81</v>
       </c>
       <c r="M3" s="26" t="s">
@@ -1863,18 +1849,18 @@
       <c r="S3" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="T3" s="29" t="s">
+      <c r="T3" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="U3" s="31" t="s">
+      <c r="U3" s="30" t="s">
         <v>91</v>
       </c>
       <c r="V3" s="26" t="s">
         <v>85</v>
       </c>
       <c r="W3" s="14">
-        <f t="shared" ref="W3:W16" ca="1" si="2">TODAY()-100</f>
-        <v>45489</v>
+        <f t="shared" ref="W3:W16" si="2">TODAY()-100</f>
+        <v>45503</v>
       </c>
       <c r="X3" s="13" t="s">
         <v>92</v>
@@ -1883,13 +1869,13 @@
         <v>93</v>
       </c>
       <c r="Z3" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AA3" s="19" t="s">
         <v>95</v>
       </c>
       <c r="AB3" s="20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC3" s="18">
         <v>880</v>
@@ -1900,15 +1886,15 @@
       <c r="AE3" s="21">
         <v>25</v>
       </c>
-      <c r="AF3" s="32" t="s">
+      <c r="AF3" s="31" t="s">
         <v>98</v>
       </c>
       <c r="AG3" s="11" t="s">
         <v>99</v>
       </c>
       <c r="AH3" s="14">
-        <f ca="1">TODAY()+200</f>
-        <v>45789</v>
+        <f>TODAY()+200</f>
+        <v>45803</v>
       </c>
       <c r="AI3" s="13" t="s">
         <v>101</v>
@@ -1917,7 +1903,7 @@
         <v>102</v>
       </c>
       <c r="AK3" s="24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AL3" s="13" t="s">
         <v>104</v>
@@ -1943,9 +1929,9 @@
       <c r="AS3" s="13">
         <v>2</v>
       </c>
-      <c r="AT3" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>16/07/2024</v>
+      <c r="AT3" s="14">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
       </c>
       <c r="AU3" s="11" t="s">
         <v>100</v>
@@ -1953,23 +1939,23 @@
       <c r="AV3" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AW3" s="29" t="s">
+      <c r="AW3" s="28" t="s">
         <v>110</v>
       </c>
       <c r="AX3" s="26" t="s">
         <v>111</v>
       </c>
       <c r="AY3" s="14">
-        <f t="shared" ref="AY3:AZ16" ca="1" si="3">TODAY()-100</f>
-        <v>45489</v>
+        <f t="shared" ref="AY3:AZ16" si="3">TODAY()-100</f>
+        <v>45503</v>
       </c>
       <c r="AZ3" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="BA3" s="14">
-        <f ca="1">TODAY()+200</f>
-        <v>45789</v>
+        <f>TODAY()+200</f>
+        <v>45803</v>
       </c>
       <c r="BB3" s="27" t="s">
         <v>81</v>
@@ -1977,110 +1963,109 @@
       <c r="BC3" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="BD3" s="28">
-        <v>1930501401662</v>
+      <c r="BD3" s="32">
+        <v>5001101452582</v>
       </c>
       <c r="BE3" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BF3" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG3" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH3" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI3" s="31">
+        <v>482025</v>
+      </c>
+      <c r="BJ3" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BG3" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH3" s="27" t="s">
+      <c r="BK3" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="BI3" s="32">
-        <f ca="1"/>
-        <v>659168</v>
-      </c>
-      <c r="BJ3" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK3" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL3" s="29" t="s">
+      <c r="BL3" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BM3" s="29" t="s">
+      <c r="BM3" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BN3" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="BO3" s="29" t="s">
+      <c r="BN3" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="BP3" s="29" t="s">
+      <c r="BO3" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="BQ3" s="29" t="s">
+      <c r="BP3" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ3" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="BR3" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS3" s="29" t="s">
+      <c r="BR3" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS3" s="28" t="s">
         <v>100</v>
       </c>
       <c r="BT3" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU3" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="BV3" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW3" s="29" t="s">
+      <c r="BV3" s="28" t="s">
         <v>122</v>
       </c>
+      <c r="BW3" s="28" t="s">
+        <v>123</v>
+      </c>
       <c r="BX3" s="26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BY3" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BZ3" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="CA3" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB3" s="26" t="s">
         <v>81</v>
       </c>
       <c r="CC3" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD3" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="4" spans="1:82" s="8" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" ht="15.65" customHeight="1" spans="1:82" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>81</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H4" s="13">
         <v>720527700</v>
@@ -2092,8 +2077,8 @@
         <v>85</v>
       </c>
       <c r="K4" s="14">
-        <f t="shared" ca="1" si="1"/>
-        <v>45489</v>
+        <f t="shared" si="1"/>
+        <v>45503</v>
       </c>
       <c r="L4" s="11" t="s">
         <v>81</v>
@@ -2129,20 +2114,20 @@
         <v>85</v>
       </c>
       <c r="W4" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>45489</v>
+        <f t="shared" si="2"/>
+        <v>45503</v>
       </c>
       <c r="X4" s="13" t="s">
         <v>92</v>
       </c>
       <c r="Y4" s="16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Z4" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AA4" s="33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AB4" s="20" t="s">
         <v>96</v>
@@ -2163,17 +2148,17 @@
         <v>99</v>
       </c>
       <c r="AH4" s="14">
-        <f t="shared" ref="AH4:AH13" ca="1" si="4">TODAY()+200</f>
-        <v>45789</v>
+        <f t="shared" ref="AH4:AH13" si="4">TODAY()+200</f>
+        <v>45803</v>
       </c>
       <c r="AI4" s="13" t="s">
         <v>101</v>
       </c>
       <c r="AJ4" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK4" s="35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AL4" s="13" t="s">
         <v>104</v>
@@ -2199,9 +2184,9 @@
       <c r="AS4" s="13">
         <v>3</v>
       </c>
-      <c r="AT4" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>16/07/2024</v>
+      <c r="AT4" s="14">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
       </c>
       <c r="AU4" s="11" t="s">
         <v>100</v>
@@ -2216,16 +2201,16 @@
         <v>111</v>
       </c>
       <c r="AY4" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="AZ4" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="BA4" s="14">
-        <f t="shared" ref="BA4:BA13" ca="1" si="5">TODAY()+200</f>
-        <v>45789</v>
+        <f t="shared" ref="BA4:BA13" si="5">TODAY()+200</f>
+        <v>45803</v>
       </c>
       <c r="BB4" s="27" t="s">
         <v>81</v>
@@ -2233,110 +2218,109 @@
       <c r="BC4" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="BD4" s="28">
-        <v>1930501097505</v>
+      <c r="BD4" s="32">
+        <v>5001101024578</v>
       </c>
       <c r="BE4" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BF4" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG4" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH4" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI4" s="31">
+        <v>961593</v>
+      </c>
+      <c r="BJ4" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BG4" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH4" s="27" t="s">
+      <c r="BK4" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="BI4" s="32">
-        <f ca="1"/>
-        <v>933285</v>
-      </c>
-      <c r="BJ4" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK4" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL4" s="29" t="s">
+      <c r="BL4" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" s="29" t="s">
+      <c r="BM4" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BN4" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="BO4" s="29" t="s">
+      <c r="BN4" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="BP4" s="29" t="s">
+      <c r="BO4" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="BQ4" s="29" t="s">
+      <c r="BP4" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ4" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="BR4" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS4" s="29" t="s">
+      <c r="BR4" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS4" s="28" t="s">
         <v>100</v>
       </c>
       <c r="BT4" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU4" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="BV4" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW4" s="30" t="s">
+      <c r="BV4" s="29" t="s">
         <v>122</v>
       </c>
+      <c r="BW4" s="29" t="s">
+        <v>123</v>
+      </c>
       <c r="BX4" s="26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BY4" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BZ4" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="CA4" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB4" s="26" t="s">
         <v>81</v>
       </c>
       <c r="CC4" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD4" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="5" spans="1:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" ht="15.65" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>81</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H5" s="13">
         <v>720527700</v>
@@ -2348,10 +2332,10 @@
         <v>85</v>
       </c>
       <c r="K5" s="14">
-        <f t="shared" ca="1" si="1"/>
-        <v>45489</v>
-      </c>
-      <c r="L5" s="29" t="s">
+        <f t="shared" si="1"/>
+        <v>45503</v>
+      </c>
+      <c r="L5" s="28" t="s">
         <v>81</v>
       </c>
       <c r="M5" s="26" t="s">
@@ -2375,33 +2359,33 @@
       <c r="S5" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="T5" s="29" t="s">
+      <c r="T5" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="U5" s="31" t="s">
+      <c r="U5" s="30" t="s">
         <v>91</v>
       </c>
       <c r="V5" s="26" t="s">
         <v>85</v>
       </c>
       <c r="W5" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>45489</v>
+        <f t="shared" si="2"/>
+        <v>45503</v>
       </c>
       <c r="X5" s="13" t="s">
         <v>92</v>
       </c>
       <c r="Y5" s="16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Z5" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AA5" s="18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AB5" s="36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC5" s="18">
         <v>880</v>
@@ -2419,17 +2403,17 @@
         <v>99</v>
       </c>
       <c r="AH5" s="14">
-        <f t="shared" ca="1" si="4"/>
-        <v>45789</v>
+        <f t="shared" si="4"/>
+        <v>45803</v>
       </c>
       <c r="AI5" s="13" t="s">
         <v>101</v>
       </c>
       <c r="AJ5" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK5" s="35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AL5" s="13" t="s">
         <v>104</v>
@@ -2455,9 +2439,9 @@
       <c r="AS5" s="13">
         <v>1</v>
       </c>
-      <c r="AT5" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>16/07/2024</v>
+      <c r="AT5" s="14">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
       </c>
       <c r="AU5" s="11" t="s">
         <v>100</v>
@@ -2465,23 +2449,23 @@
       <c r="AV5" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AW5" s="29" t="s">
+      <c r="AW5" s="28" t="s">
         <v>110</v>
       </c>
       <c r="AX5" s="26" t="s">
         <v>111</v>
       </c>
       <c r="AY5" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="AZ5" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="BA5" s="14">
-        <f t="shared" ca="1" si="5"/>
-        <v>45789</v>
+        <f t="shared" si="5"/>
+        <v>45803</v>
       </c>
       <c r="BB5" s="27" t="s">
         <v>81</v>
@@ -2489,110 +2473,109 @@
       <c r="BC5" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="BD5" s="28">
-        <v>1930501276700</v>
+      <c r="BD5" s="32">
+        <v>5001101186633</v>
       </c>
       <c r="BE5" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BF5" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG5" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH5" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI5" s="31">
+        <v>501227</v>
+      </c>
+      <c r="BJ5" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BG5" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH5" s="27" t="s">
+      <c r="BK5" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="BI5" s="32">
-        <f ca="1"/>
-        <v>774365</v>
-      </c>
-      <c r="BJ5" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK5" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL5" s="29" t="s">
+      <c r="BL5" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" s="29" t="s">
+      <c r="BM5" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BN5" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="BO5" s="29" t="s">
+      <c r="BN5" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="BP5" s="29" t="s">
+      <c r="BO5" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="BQ5" s="29" t="s">
+      <c r="BP5" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ5" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="BR5" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS5" s="29" t="s">
+      <c r="BR5" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS5" s="28" t="s">
         <v>100</v>
       </c>
       <c r="BT5" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU5" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="BV5" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW5" s="29" t="s">
+      <c r="BV5" s="28" t="s">
         <v>122</v>
       </c>
+      <c r="BW5" s="28" t="s">
+        <v>123</v>
+      </c>
       <c r="BX5" s="26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BY5" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BZ5" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="CA5" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB5" s="26" t="s">
         <v>81</v>
       </c>
       <c r="CC5" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD5" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:82" s="8" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" ht="15.65" customHeight="1" spans="1:82" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>81</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H6" s="13">
         <v>720527700</v>
@@ -2604,8 +2587,8 @@
         <v>85</v>
       </c>
       <c r="K6" s="14">
-        <f t="shared" ca="1" si="1"/>
-        <v>45489</v>
+        <f t="shared" si="1"/>
+        <v>45503</v>
       </c>
       <c r="L6" s="11" t="s">
         <v>81</v>
@@ -2641,20 +2624,20 @@
         <v>85</v>
       </c>
       <c r="W6" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>45489</v>
+        <f t="shared" si="2"/>
+        <v>45503</v>
       </c>
       <c r="X6" s="13" t="s">
         <v>92</v>
       </c>
       <c r="Y6" s="16" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Z6" s="18" t="s">
         <v>94</v>
       </c>
       <c r="AA6" s="18" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AB6" s="36" t="s">
         <v>96</v>
@@ -2681,10 +2664,10 @@
         <v>101</v>
       </c>
       <c r="AJ6" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK6" s="35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AL6" s="13" t="s">
         <v>104</v>
@@ -2710,9 +2693,9 @@
       <c r="AS6" s="13">
         <v>2</v>
       </c>
-      <c r="AT6" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>16/07/2024</v>
+      <c r="AT6" s="14">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
       </c>
       <c r="AU6" s="11" t="s">
         <v>100</v>
@@ -2727,12 +2710,12 @@
         <v>111</v>
       </c>
       <c r="AY6" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="AZ6" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="BA6" s="23" t="str">
         <f t="shared" ref="BA6:BA15" si="6">AH6</f>
@@ -2744,110 +2727,109 @@
       <c r="BC6" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="BD6" s="28">
-        <v>1930501126056</v>
+      <c r="BD6" s="32">
+        <v>5001101175570</v>
       </c>
       <c r="BE6" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BF6" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG6" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH6" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI6" s="31">
+        <v>132058</v>
+      </c>
+      <c r="BJ6" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BG6" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH6" s="27" t="s">
+      <c r="BK6" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="BI6" s="32">
-        <f ca="1"/>
-        <v>550356</v>
-      </c>
-      <c r="BJ6" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK6" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL6" s="29" t="s">
+      <c r="BL6" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" s="29" t="s">
+      <c r="BM6" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BN6" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="BO6" s="29" t="s">
+      <c r="BN6" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="BP6" s="29" t="s">
+      <c r="BO6" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="BQ6" s="29" t="s">
+      <c r="BP6" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ6" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="BR6" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS6" s="29" t="s">
+      <c r="BR6" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS6" s="28" t="s">
         <v>100</v>
       </c>
       <c r="BT6" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU6" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="BV6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW6" s="30" t="s">
+      <c r="BV6" s="29" t="s">
         <v>122</v>
       </c>
+      <c r="BW6" s="29" t="s">
+        <v>123</v>
+      </c>
       <c r="BX6" s="26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BY6" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BZ6" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="CA6" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB6" s="26" t="s">
         <v>81</v>
       </c>
       <c r="CC6" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD6" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:82" s="8" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" ht="15.65" customHeight="1" spans="1:82" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>81</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H7" s="13">
         <v>720527700</v>
@@ -2859,10 +2841,10 @@
         <v>85</v>
       </c>
       <c r="K7" s="14">
-        <f t="shared" ca="1" si="1"/>
-        <v>45489</v>
-      </c>
-      <c r="L7" s="29" t="s">
+        <f t="shared" si="1"/>
+        <v>45503</v>
+      </c>
+      <c r="L7" s="28" t="s">
         <v>81</v>
       </c>
       <c r="M7" s="26" t="s">
@@ -2886,33 +2868,33 @@
       <c r="S7" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="T7" s="29" t="s">
+      <c r="T7" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="U7" s="31" t="s">
+      <c r="U7" s="30" t="s">
         <v>91</v>
       </c>
       <c r="V7" s="26" t="s">
         <v>85</v>
       </c>
       <c r="W7" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>45489</v>
+        <f t="shared" si="2"/>
+        <v>45503</v>
       </c>
       <c r="X7" s="13" t="s">
         <v>92</v>
       </c>
       <c r="Y7" s="16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Z7" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AA7" s="18" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AB7" s="38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC7" s="18">
         <v>880</v>
@@ -2930,17 +2912,17 @@
         <v>99</v>
       </c>
       <c r="AH7" s="14">
-        <f t="shared" ca="1" si="4"/>
-        <v>45789</v>
+        <f t="shared" si="4"/>
+        <v>45803</v>
       </c>
       <c r="AI7" s="13" t="s">
         <v>101</v>
       </c>
       <c r="AJ7" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK7" s="35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AL7" s="13" t="s">
         <v>104</v>
@@ -2966,9 +2948,9 @@
       <c r="AS7" s="13">
         <v>3</v>
       </c>
-      <c r="AT7" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>16/07/2024</v>
+      <c r="AT7" s="14">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
       </c>
       <c r="AU7" s="11" t="s">
         <v>100</v>
@@ -2976,23 +2958,23 @@
       <c r="AV7" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AW7" s="29" t="s">
+      <c r="AW7" s="28" t="s">
         <v>110</v>
       </c>
       <c r="AX7" s="26" t="s">
         <v>111</v>
       </c>
       <c r="AY7" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="AZ7" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="BA7" s="14">
-        <f t="shared" ca="1" si="5"/>
-        <v>45789</v>
+        <f t="shared" si="5"/>
+        <v>45803</v>
       </c>
       <c r="BB7" s="27" t="s">
         <v>81</v>
@@ -3000,110 +2982,109 @@
       <c r="BC7" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="BD7" s="28">
-        <v>1930501051847</v>
+      <c r="BD7" s="32">
+        <v>5001101346731</v>
       </c>
       <c r="BE7" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BF7" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG7" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH7" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI7" s="31">
+        <v>246802</v>
+      </c>
+      <c r="BJ7" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BG7" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH7" s="27" t="s">
+      <c r="BK7" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="BI7" s="32">
-        <f ca="1"/>
-        <v>419853</v>
-      </c>
-      <c r="BJ7" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK7" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL7" s="29" t="s">
+      <c r="BL7" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BM7" s="29" t="s">
+      <c r="BM7" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BN7" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="BO7" s="29" t="s">
+      <c r="BN7" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="BP7" s="29" t="s">
+      <c r="BO7" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="BQ7" s="29" t="s">
+      <c r="BP7" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ7" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="BR7" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS7" s="29" t="s">
+      <c r="BR7" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS7" s="28" t="s">
         <v>100</v>
       </c>
       <c r="BT7" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU7" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="BV7" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW7" s="29" t="s">
+      <c r="BV7" s="28" t="s">
         <v>122</v>
       </c>
+      <c r="BW7" s="28" t="s">
+        <v>123</v>
+      </c>
       <c r="BX7" s="26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BY7" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BZ7" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="CA7" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB7" s="26" t="s">
         <v>81</v>
       </c>
       <c r="CC7" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD7" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="8" spans="1:82" s="8" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" ht="15.65" customHeight="1" spans="1:82" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>166</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>81</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H8" s="13">
         <v>720527700</v>
@@ -3115,8 +3096,8 @@
         <v>85</v>
       </c>
       <c r="K8" s="14">
-        <f t="shared" ca="1" si="1"/>
-        <v>45489</v>
+        <f t="shared" si="1"/>
+        <v>45503</v>
       </c>
       <c r="L8" s="11" t="s">
         <v>81</v>
@@ -3152,20 +3133,20 @@
         <v>85</v>
       </c>
       <c r="W8" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>45489</v>
+        <f t="shared" si="2"/>
+        <v>45503</v>
       </c>
       <c r="X8" s="13" t="s">
         <v>92</v>
       </c>
       <c r="Y8" s="16" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Z8" s="18" t="s">
         <v>94</v>
       </c>
       <c r="AA8" s="18" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AB8" s="38" t="s">
         <v>96</v>
@@ -3192,10 +3173,10 @@
         <v>101</v>
       </c>
       <c r="AJ8" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK8" s="35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AL8" s="13" t="s">
         <v>104</v>
@@ -3221,9 +3202,9 @@
       <c r="AS8" s="13">
         <v>1</v>
       </c>
-      <c r="AT8" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>16/07/2024</v>
+      <c r="AT8" s="14">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
       </c>
       <c r="AU8" s="11" t="s">
         <v>100</v>
@@ -3238,12 +3219,12 @@
         <v>111</v>
       </c>
       <c r="AY8" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="AZ8" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="BA8" s="23" t="str">
         <f t="shared" si="6"/>
@@ -3255,110 +3236,109 @@
       <c r="BC8" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="BD8" s="28">
-        <v>1930501438958</v>
+      <c r="BD8" s="32">
+        <v>5001101258410</v>
       </c>
       <c r="BE8" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BF8" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG8" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH8" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI8" s="31">
+        <v>850214</v>
+      </c>
+      <c r="BJ8" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BG8" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH8" s="27" t="s">
+      <c r="BK8" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="BI8" s="32">
-        <f ca="1"/>
-        <v>266635</v>
-      </c>
-      <c r="BJ8" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK8" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL8" s="29" t="s">
+      <c r="BL8" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BM8" s="29" t="s">
+      <c r="BM8" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BN8" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="BO8" s="29" t="s">
+      <c r="BN8" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="BP8" s="29" t="s">
+      <c r="BO8" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="BQ8" s="29" t="s">
+      <c r="BP8" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ8" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="BR8" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS8" s="29" t="s">
+      <c r="BR8" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS8" s="28" t="s">
         <v>100</v>
       </c>
       <c r="BT8" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU8" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="BV8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW8" s="30" t="s">
+      <c r="BV8" s="29" t="s">
         <v>122</v>
       </c>
+      <c r="BW8" s="29" t="s">
+        <v>123</v>
+      </c>
       <c r="BX8" s="26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BY8" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BZ8" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="CA8" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB8" s="26" t="s">
         <v>81</v>
       </c>
       <c r="CC8" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD8" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:82" s="8" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" ht="15.65" customHeight="1" spans="1:82" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>81</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H9" s="13">
         <v>720527700</v>
@@ -3370,10 +3350,10 @@
         <v>85</v>
       </c>
       <c r="K9" s="14">
-        <f t="shared" ca="1" si="1"/>
-        <v>45489</v>
-      </c>
-      <c r="L9" s="29" t="s">
+        <f t="shared" si="1"/>
+        <v>45503</v>
+      </c>
+      <c r="L9" s="28" t="s">
         <v>81</v>
       </c>
       <c r="M9" s="26" t="s">
@@ -3397,33 +3377,33 @@
       <c r="S9" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="T9" s="29" t="s">
+      <c r="T9" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="U9" s="31" t="s">
+      <c r="U9" s="30" t="s">
         <v>91</v>
       </c>
       <c r="V9" s="26" t="s">
         <v>85</v>
       </c>
       <c r="W9" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>45489</v>
+        <f t="shared" si="2"/>
+        <v>45503</v>
       </c>
       <c r="X9" s="13" t="s">
         <v>92</v>
       </c>
       <c r="Y9" s="16" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Z9" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AA9" s="18" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AB9" s="36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC9" s="18">
         <v>880</v>
@@ -3441,17 +3421,17 @@
         <v>99</v>
       </c>
       <c r="AH9" s="14">
-        <f t="shared" ca="1" si="4"/>
-        <v>45789</v>
+        <f t="shared" si="4"/>
+        <v>45803</v>
       </c>
       <c r="AI9" s="13" t="s">
         <v>101</v>
       </c>
       <c r="AJ9" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK9" s="35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AL9" s="13" t="s">
         <v>104</v>
@@ -3477,9 +3457,9 @@
       <c r="AS9" s="13">
         <v>2</v>
       </c>
-      <c r="AT9" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>16/07/2024</v>
+      <c r="AT9" s="14">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
       </c>
       <c r="AU9" s="11" t="s">
         <v>100</v>
@@ -3487,23 +3467,23 @@
       <c r="AV9" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AW9" s="29" t="s">
+      <c r="AW9" s="28" t="s">
         <v>110</v>
       </c>
       <c r="AX9" s="26" t="s">
         <v>111</v>
       </c>
       <c r="AY9" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="AZ9" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="BA9" s="14">
-        <f t="shared" ca="1" si="5"/>
-        <v>45789</v>
+        <f t="shared" si="5"/>
+        <v>45803</v>
       </c>
       <c r="BB9" s="27" t="s">
         <v>81</v>
@@ -3511,95 +3491,94 @@
       <c r="BC9" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="BD9" s="28">
-        <v>1930701412351</v>
+      <c r="BD9" s="32">
+        <v>5001101101679</v>
       </c>
       <c r="BE9" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BF9" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG9" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH9" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI9" s="31">
+        <v>173057</v>
+      </c>
+      <c r="BJ9" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BG9" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH9" s="27" t="s">
+      <c r="BK9" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="BI9" s="32">
-        <f ca="1"/>
-        <v>213268</v>
-      </c>
-      <c r="BJ9" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK9" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL9" s="29" t="s">
+      <c r="BL9" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BM9" s="29" t="s">
+      <c r="BM9" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BN9" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="BO9" s="29" t="s">
+      <c r="BN9" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="BP9" s="29" t="s">
+      <c r="BO9" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="BQ9" s="29" t="s">
+      <c r="BP9" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ9" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="BR9" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS9" s="29" t="s">
+      <c r="BR9" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS9" s="28" t="s">
         <v>100</v>
       </c>
       <c r="BT9" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU9" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="BV9" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW9" s="29" t="s">
+      <c r="BV9" s="28" t="s">
         <v>122</v>
       </c>
+      <c r="BW9" s="28" t="s">
+        <v>123</v>
+      </c>
       <c r="BX9" s="26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BY9" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BZ9" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="CA9" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB9" s="26" t="s">
         <v>81</v>
       </c>
       <c r="CC9" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD9" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="10" spans="1:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" ht="15.65" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>79</v>
@@ -3611,10 +3590,10 @@
         <v>81</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H10" s="13">
         <v>720527700</v>
@@ -3626,8 +3605,8 @@
         <v>85</v>
       </c>
       <c r="K10" s="14">
-        <f t="shared" ca="1" si="1"/>
-        <v>45489</v>
+        <f t="shared" si="1"/>
+        <v>45503</v>
       </c>
       <c r="L10" s="11" t="s">
         <v>81</v>
@@ -3663,8 +3642,8 @@
         <v>85</v>
       </c>
       <c r="W10" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>45489</v>
+        <f t="shared" si="2"/>
+        <v>45503</v>
       </c>
       <c r="X10" s="13" t="s">
         <v>92</v>
@@ -3676,7 +3655,7 @@
         <v>94</v>
       </c>
       <c r="AA10" s="18" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AB10" s="36" t="s">
         <v>96</v>
@@ -3706,7 +3685,7 @@
         <v>102</v>
       </c>
       <c r="AK10" s="24" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AL10" s="13" t="s">
         <v>104</v>
@@ -3727,14 +3706,14 @@
         <v>109</v>
       </c>
       <c r="AR10" s="13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AS10" s="13">
         <v>3</v>
       </c>
-      <c r="AT10" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>16/07/2024</v>
+      <c r="AT10" s="14">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
       </c>
       <c r="AU10" s="11" t="s">
         <v>100</v>
@@ -3742,19 +3721,19 @@
       <c r="AV10" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AW10" s="29" t="s">
+      <c r="AW10" s="28" t="s">
         <v>110</v>
       </c>
       <c r="AX10" s="26" t="s">
         <v>111</v>
       </c>
       <c r="AY10" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="AZ10" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="BA10" s="39" t="str">
         <f t="shared" si="6"/>
@@ -3766,98 +3745,97 @@
       <c r="BC10" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="BD10" s="28">
-        <v>1930501235621</v>
+      <c r="BD10" s="32">
+        <v>5001101123140</v>
       </c>
       <c r="BE10" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BF10" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG10" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH10" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI10" s="31">
+        <v>457306</v>
+      </c>
+      <c r="BJ10" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BG10" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH10" s="27" t="s">
+      <c r="BK10" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="BI10" s="32">
-        <f ca="1"/>
-        <v>161790</v>
-      </c>
-      <c r="BJ10" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK10" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL10" s="29" t="s">
+      <c r="BL10" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BM10" s="29" t="s">
+      <c r="BM10" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BN10" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="BO10" s="29" t="s">
+      <c r="BN10" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="BP10" s="29" t="s">
+      <c r="BO10" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="BQ10" s="29" t="s">
+      <c r="BP10" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ10" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="BR10" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS10" s="29" t="s">
+      <c r="BR10" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS10" s="28" t="s">
         <v>100</v>
       </c>
       <c r="BT10" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU10" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="BV10" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW10" s="29" t="s">
+      <c r="BV10" s="28" t="s">
         <v>122</v>
       </c>
+      <c r="BW10" s="28" t="s">
+        <v>123</v>
+      </c>
       <c r="BX10" s="26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BY10" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BZ10" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="CA10" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB10" s="26" t="s">
         <v>81</v>
       </c>
       <c r="CC10" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD10" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" ht="15.65" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>80</v>
@@ -3866,10 +3844,10 @@
         <v>81</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H11" s="13">
         <v>720527700</v>
@@ -3881,10 +3859,10 @@
         <v>85</v>
       </c>
       <c r="K11" s="14">
-        <f t="shared" ca="1" si="1"/>
-        <v>45489</v>
-      </c>
-      <c r="L11" s="29" t="s">
+        <f t="shared" si="1"/>
+        <v>45503</v>
+      </c>
+      <c r="L11" s="28" t="s">
         <v>81</v>
       </c>
       <c r="M11" s="26" t="s">
@@ -3908,18 +3886,18 @@
       <c r="S11" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="T11" s="29" t="s">
+      <c r="T11" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="U11" s="31" t="s">
+      <c r="U11" s="30" t="s">
         <v>91</v>
       </c>
       <c r="V11" s="26" t="s">
         <v>85</v>
       </c>
       <c r="W11" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>45489</v>
+        <f t="shared" si="2"/>
+        <v>45503</v>
       </c>
       <c r="X11" s="13" t="s">
         <v>92</v>
@@ -3928,13 +3906,13 @@
         <v>93</v>
       </c>
       <c r="Z11" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AA11" s="18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AB11" s="36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC11" s="18">
         <v>880</v>
@@ -3952,8 +3930,8 @@
         <v>99</v>
       </c>
       <c r="AH11" s="14">
-        <f t="shared" ca="1" si="4"/>
-        <v>45789</v>
+        <f t="shared" si="4"/>
+        <v>45803</v>
       </c>
       <c r="AI11" s="13" t="s">
         <v>101</v>
@@ -3962,7 +3940,7 @@
         <v>102</v>
       </c>
       <c r="AK11" s="24" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL11" s="13" t="s">
         <v>104</v>
@@ -3983,14 +3961,14 @@
         <v>109</v>
       </c>
       <c r="AR11" s="13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AS11" s="13">
         <v>1</v>
       </c>
-      <c r="AT11" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>16/07/2024</v>
+      <c r="AT11" s="14">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
       </c>
       <c r="AU11" s="11" t="s">
         <v>100</v>
@@ -3998,23 +3976,23 @@
       <c r="AV11" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AW11" s="29" t="s">
+      <c r="AW11" s="28" t="s">
         <v>110</v>
       </c>
       <c r="AX11" s="26" t="s">
         <v>111</v>
       </c>
       <c r="AY11" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="AZ11" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="BA11" s="14">
-        <f t="shared" ca="1" si="5"/>
-        <v>45789</v>
+        <f t="shared" si="5"/>
+        <v>45803</v>
       </c>
       <c r="BB11" s="27" t="s">
         <v>81</v>
@@ -4022,95 +4000,94 @@
       <c r="BC11" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="BD11" s="28">
-        <v>1930701323841</v>
+      <c r="BD11" s="32">
+        <v>5001101113362</v>
       </c>
       <c r="BE11" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BF11" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG11" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH11" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI11" s="31">
+        <v>282326</v>
+      </c>
+      <c r="BJ11" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BG11" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH11" s="27" t="s">
+      <c r="BK11" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="BI11" s="32">
-        <f ca="1"/>
-        <v>133609</v>
-      </c>
-      <c r="BJ11" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK11" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL11" s="29" t="s">
+      <c r="BL11" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BM11" s="29" t="s">
+      <c r="BM11" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BN11" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="BO11" s="29" t="s">
+      <c r="BN11" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="BP11" s="29" t="s">
+      <c r="BO11" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="BQ11" s="29" t="s">
+      <c r="BP11" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ11" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="BR11" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS11" s="29" t="s">
+      <c r="BR11" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS11" s="28" t="s">
         <v>100</v>
       </c>
       <c r="BT11" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU11" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="BV11" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW11" s="29" t="s">
+      <c r="BV11" s="28" t="s">
         <v>122</v>
       </c>
+      <c r="BW11" s="28" t="s">
+        <v>123</v>
+      </c>
       <c r="BX11" s="26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BY11" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BZ11" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="CA11" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB11" s="26" t="s">
         <v>81</v>
       </c>
       <c r="CC11" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD11" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="12" spans="1:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" ht="15.65" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>79</v>
@@ -4122,10 +4099,10 @@
         <v>81</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H12" s="13">
         <v>720527700</v>
@@ -4137,8 +4114,8 @@
         <v>85</v>
       </c>
       <c r="K12" s="14">
-        <f t="shared" ca="1" si="1"/>
-        <v>45489</v>
+        <f t="shared" si="1"/>
+        <v>45503</v>
       </c>
       <c r="L12" s="11" t="s">
         <v>81</v>
@@ -4174,8 +4151,8 @@
         <v>85</v>
       </c>
       <c r="W12" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>45489</v>
+        <f t="shared" si="2"/>
+        <v>45503</v>
       </c>
       <c r="X12" s="13" t="s">
         <v>92</v>
@@ -4187,7 +4164,7 @@
         <v>94</v>
       </c>
       <c r="AA12" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AB12" s="36" t="s">
         <v>96</v>
@@ -4217,7 +4194,7 @@
         <v>102</v>
       </c>
       <c r="AK12" s="24" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AL12" s="13" t="s">
         <v>104</v>
@@ -4238,14 +4215,14 @@
         <v>106</v>
       </c>
       <c r="AR12" s="13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AS12" s="13">
         <v>2</v>
       </c>
-      <c r="AT12" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>16/07/2024</v>
+      <c r="AT12" s="14">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
       </c>
       <c r="AU12" s="11" t="s">
         <v>100</v>
@@ -4253,19 +4230,19 @@
       <c r="AV12" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AW12" s="29" t="s">
+      <c r="AW12" s="28" t="s">
         <v>110</v>
       </c>
       <c r="AX12" s="26" t="s">
         <v>111</v>
       </c>
       <c r="AY12" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="AZ12" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="BA12" s="39" t="str">
         <f t="shared" si="6"/>
@@ -4277,98 +4254,97 @@
       <c r="BC12" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="BD12" s="28">
-        <v>1930501371845</v>
+      <c r="BD12" s="32">
+        <v>5001101336257</v>
       </c>
       <c r="BE12" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BF12" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG12" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH12" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI12" s="31">
+        <v>434112</v>
+      </c>
+      <c r="BJ12" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BG12" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH12" s="27" t="s">
+      <c r="BK12" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="BI12" s="32">
-        <f ca="1"/>
-        <v>391568</v>
-      </c>
-      <c r="BJ12" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK12" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL12" s="29" t="s">
+      <c r="BL12" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BM12" s="29" t="s">
+      <c r="BM12" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BN12" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="BO12" s="29" t="s">
+      <c r="BN12" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="BP12" s="29" t="s">
+      <c r="BO12" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="BQ12" s="29" t="s">
+      <c r="BP12" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ12" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="BR12" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS12" s="29" t="s">
+      <c r="BR12" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS12" s="28" t="s">
         <v>100</v>
       </c>
       <c r="BT12" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU12" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="BV12" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW12" s="29" t="s">
+      <c r="BV12" s="28" t="s">
         <v>122</v>
       </c>
+      <c r="BW12" s="28" t="s">
+        <v>123</v>
+      </c>
       <c r="BX12" s="26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BY12" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BZ12" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="CA12" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB12" s="26" t="s">
         <v>81</v>
       </c>
       <c r="CC12" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD12" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="13" spans="1:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" ht="15.65" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>79</v>
+        <v>196</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>154</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>80</v>
@@ -4377,10 +4353,10 @@
         <v>81</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H13" s="13">
         <v>720527700</v>
@@ -4392,10 +4368,10 @@
         <v>85</v>
       </c>
       <c r="K13" s="14">
-        <f t="shared" ca="1" si="1"/>
-        <v>45489</v>
-      </c>
-      <c r="L13" s="29" t="s">
+        <f t="shared" si="1"/>
+        <v>45503</v>
+      </c>
+      <c r="L13" s="28" t="s">
         <v>81</v>
       </c>
       <c r="M13" s="26" t="s">
@@ -4419,18 +4395,18 @@
       <c r="S13" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="T13" s="29" t="s">
+      <c r="T13" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="U13" s="31" t="s">
+      <c r="U13" s="30" t="s">
         <v>91</v>
       </c>
       <c r="V13" s="26" t="s">
         <v>85</v>
       </c>
       <c r="W13" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>45489</v>
+        <f t="shared" si="2"/>
+        <v>45503</v>
       </c>
       <c r="X13" s="13" t="s">
         <v>92</v>
@@ -4439,13 +4415,13 @@
         <v>93</v>
       </c>
       <c r="Z13" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AA13" s="18" t="s">
         <v>95</v>
       </c>
       <c r="AB13" s="36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC13" s="18">
         <v>880</v>
@@ -4463,8 +4439,8 @@
         <v>99</v>
       </c>
       <c r="AH13" s="14">
-        <f t="shared" ca="1" si="4"/>
-        <v>45789</v>
+        <f t="shared" si="4"/>
+        <v>45803</v>
       </c>
       <c r="AI13" s="13" t="s">
         <v>101</v>
@@ -4473,7 +4449,7 @@
         <v>102</v>
       </c>
       <c r="AK13" s="24" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AL13" s="13" t="s">
         <v>104</v>
@@ -4494,14 +4470,14 @@
         <v>109</v>
       </c>
       <c r="AR13" s="13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AS13" s="13">
         <v>3</v>
       </c>
-      <c r="AT13" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>16/07/2024</v>
+      <c r="AT13" s="14">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
       </c>
       <c r="AU13" s="11" t="s">
         <v>100</v>
@@ -4509,23 +4485,23 @@
       <c r="AV13" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AW13" s="29" t="s">
+      <c r="AW13" s="28" t="s">
         <v>110</v>
       </c>
       <c r="AX13" s="26" t="s">
         <v>111</v>
       </c>
       <c r="AY13" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="AZ13" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="BA13" s="14">
-        <f t="shared" ca="1" si="5"/>
-        <v>45789</v>
+        <f t="shared" si="5"/>
+        <v>45803</v>
       </c>
       <c r="BB13" s="27" t="s">
         <v>81</v>
@@ -4533,98 +4509,97 @@
       <c r="BC13" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="BD13" s="28">
-        <v>1930701297683</v>
+      <c r="BD13" s="32">
+        <v>5001101452478</v>
       </c>
       <c r="BE13" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BF13" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG13" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH13" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI13" s="31">
+        <v>626819</v>
+      </c>
+      <c r="BJ13" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BG13" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH13" s="27" t="s">
+      <c r="BK13" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="BI13" s="32">
-        <f ca="1"/>
-        <v>484178</v>
-      </c>
-      <c r="BJ13" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK13" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL13" s="29" t="s">
+      <c r="BL13" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BM13" s="29" t="s">
+      <c r="BM13" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BN13" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="BO13" s="29" t="s">
+      <c r="BN13" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="BP13" s="29" t="s">
+      <c r="BO13" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="BQ13" s="29" t="s">
+      <c r="BP13" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ13" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="BR13" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS13" s="29" t="s">
+      <c r="BR13" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS13" s="28" t="s">
         <v>100</v>
       </c>
       <c r="BT13" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU13" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="BV13" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW13" s="29" t="s">
+      <c r="BV13" s="28" t="s">
         <v>122</v>
       </c>
+      <c r="BW13" s="28" t="s">
+        <v>123</v>
+      </c>
       <c r="BX13" s="26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BY13" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BZ13" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="CA13" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB13" s="26" t="s">
         <v>81</v>
       </c>
       <c r="CC13" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD13" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" ht="15.65" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B14" s="40" t="s">
         <v>200</v>
       </c>
+      <c r="B14" s="41" t="s">
+        <v>201</v>
+      </c>
       <c r="C14" s="1" t="s">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>80</v>
@@ -4633,10 +4608,10 @@
         <v>81</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H14" s="13">
         <v>720527700</v>
@@ -4648,8 +4623,8 @@
         <v>85</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" ca="1" si="1"/>
-        <v>45489</v>
+        <f t="shared" si="1"/>
+        <v>45503</v>
       </c>
       <c r="L14" s="11" t="s">
         <v>81</v>
@@ -4685,8 +4660,8 @@
         <v>85</v>
       </c>
       <c r="W14" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>45489</v>
+        <f t="shared" si="2"/>
+        <v>45503</v>
       </c>
       <c r="X14" s="13" t="s">
         <v>92</v>
@@ -4701,7 +4676,7 @@
         <v>95</v>
       </c>
       <c r="AB14" s="36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC14" s="18">
         <v>880</v>
@@ -4728,7 +4703,7 @@
         <v>102</v>
       </c>
       <c r="AK14" s="24" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AL14" s="13" t="s">
         <v>104</v>
@@ -4749,14 +4724,14 @@
         <v>106</v>
       </c>
       <c r="AR14" s="13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AS14" s="13">
         <v>1</v>
       </c>
-      <c r="AT14" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>16/07/2024</v>
+      <c r="AT14" s="14">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
       </c>
       <c r="AU14" s="11" t="s">
         <v>100</v>
@@ -4764,19 +4739,19 @@
       <c r="AV14" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AW14" s="29" t="s">
+      <c r="AW14" s="28" t="s">
         <v>110</v>
       </c>
       <c r="AX14" s="26" t="s">
         <v>111</v>
       </c>
       <c r="AY14" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="AZ14" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="BA14" s="39" t="str">
         <f t="shared" si="6"/>
@@ -4788,110 +4763,109 @@
       <c r="BC14" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="BD14" s="28">
-        <v>1930501444001</v>
+      <c r="BD14" s="32">
+        <v>5001101459307</v>
       </c>
       <c r="BE14" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BF14" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG14" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH14" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI14" s="31">
+        <v>579774</v>
+      </c>
+      <c r="BJ14" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BG14" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH14" s="27" t="s">
+      <c r="BK14" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="BI14" s="32">
-        <f ca="1"/>
-        <v>770853</v>
-      </c>
-      <c r="BJ14" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK14" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL14" s="29" t="s">
+      <c r="BL14" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BM14" s="29" t="s">
+      <c r="BM14" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BN14" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="BO14" s="29" t="s">
+      <c r="BN14" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="BP14" s="29" t="s">
+      <c r="BO14" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="BQ14" s="29" t="s">
+      <c r="BP14" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ14" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="BR14" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS14" s="29" t="s">
+      <c r="BR14" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS14" s="28" t="s">
         <v>100</v>
       </c>
       <c r="BT14" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU14" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="BV14" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW14" s="29" t="s">
+      <c r="BV14" s="28" t="s">
         <v>122</v>
       </c>
+      <c r="BW14" s="28" t="s">
+        <v>123</v>
+      </c>
       <c r="BX14" s="26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BY14" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BZ14" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="CA14" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB14" s="26" t="s">
         <v>81</v>
       </c>
       <c r="CC14" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD14" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:82" s="8" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" ht="15.65" customHeight="1" spans="1:82" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>81</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H15" s="13">
         <v>720527700</v>
@@ -4903,10 +4877,10 @@
         <v>85</v>
       </c>
       <c r="K15" s="14">
-        <f t="shared" ca="1" si="1"/>
-        <v>45489</v>
-      </c>
-      <c r="L15" s="29" t="s">
+        <f t="shared" si="1"/>
+        <v>45503</v>
+      </c>
+      <c r="L15" s="28" t="s">
         <v>81</v>
       </c>
       <c r="M15" s="26" t="s">
@@ -4930,33 +4904,33 @@
       <c r="S15" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="T15" s="29" t="s">
+      <c r="T15" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="U15" s="31" t="s">
+      <c r="U15" s="30" t="s">
         <v>91</v>
       </c>
       <c r="V15" s="26" t="s">
         <v>85</v>
       </c>
       <c r="W15" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>45489</v>
+        <f t="shared" si="2"/>
+        <v>45503</v>
       </c>
       <c r="X15" s="13" t="s">
         <v>92</v>
       </c>
       <c r="Y15" s="16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Z15" s="18" t="s">
         <v>94</v>
       </c>
       <c r="AA15" s="18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AB15" s="36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC15" s="18">
         <v>880</v>
@@ -4980,10 +4954,10 @@
         <v>101</v>
       </c>
       <c r="AJ15" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK15" s="35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AL15" s="13" t="s">
         <v>104</v>
@@ -5004,14 +4978,14 @@
         <v>109</v>
       </c>
       <c r="AR15" s="13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AS15" s="13">
         <v>2</v>
       </c>
-      <c r="AT15" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>16/07/2024</v>
+      <c r="AT15" s="14">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
       </c>
       <c r="AU15" s="11" t="s">
         <v>100</v>
@@ -5019,19 +4993,19 @@
       <c r="AV15" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AW15" s="29" t="s">
+      <c r="AW15" s="28" t="s">
         <v>110</v>
       </c>
       <c r="AX15" s="26" t="s">
         <v>111</v>
       </c>
       <c r="AY15" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="AZ15" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="BA15" s="39" t="str">
         <f t="shared" si="6"/>
@@ -5043,95 +5017,94 @@
       <c r="BC15" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="BD15" s="28">
-        <v>1930701018354</v>
+      <c r="BD15" s="32">
+        <v>5001101073652</v>
       </c>
       <c r="BE15" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BF15" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG15" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH15" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI15" s="31">
+        <v>533548</v>
+      </c>
+      <c r="BJ15" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BG15" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH15" s="27" t="s">
+      <c r="BK15" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="BI15" s="32">
-        <f ca="1"/>
-        <v>541504</v>
-      </c>
-      <c r="BJ15" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK15" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL15" s="29" t="s">
+      <c r="BL15" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BM15" s="29" t="s">
+      <c r="BM15" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BN15" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="BO15" s="29" t="s">
+      <c r="BN15" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="BP15" s="29" t="s">
+      <c r="BO15" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="BQ15" s="29" t="s">
+      <c r="BP15" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ15" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="BR15" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS15" s="29" t="s">
+      <c r="BR15" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS15" s="28" t="s">
         <v>100</v>
       </c>
       <c r="BT15" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU15" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="BV15" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW15" s="29" t="s">
+      <c r="BV15" s="28" t="s">
         <v>122</v>
       </c>
+      <c r="BW15" s="28" t="s">
+        <v>123</v>
+      </c>
       <c r="BX15" s="26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BY15" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BZ15" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="CA15" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB15" s="26" t="s">
         <v>81</v>
       </c>
       <c r="CC15" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD15" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="16" spans="1:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" ht="15.65" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>79</v>
@@ -5143,10 +5116,10 @@
         <v>81</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H16" s="13">
         <v>720527700</v>
@@ -5158,8 +5131,8 @@
         <v>85</v>
       </c>
       <c r="K16" s="14">
-        <f t="shared" ca="1" si="1"/>
-        <v>45489</v>
+        <f t="shared" si="1"/>
+        <v>45503</v>
       </c>
       <c r="L16" s="11" t="s">
         <v>81</v>
@@ -5195,8 +5168,8 @@
         <v>85</v>
       </c>
       <c r="W16" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>45489</v>
+        <f t="shared" si="2"/>
+        <v>45503</v>
       </c>
       <c r="X16" s="13" t="s">
         <v>92</v>
@@ -5205,13 +5178,13 @@
         <v>93</v>
       </c>
       <c r="Z16" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AA16" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AB16" s="36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC16" s="18">
         <v>880</v>
@@ -5229,8 +5202,8 @@
         <v>99</v>
       </c>
       <c r="AH16" s="14">
-        <f t="shared" ref="AH16" ca="1" si="7">TODAY()+200</f>
-        <v>45789</v>
+        <f t="shared" ref="AH16" si="7">TODAY()+200</f>
+        <v>45803</v>
       </c>
       <c r="AI16" s="13" t="s">
         <v>101</v>
@@ -5239,7 +5212,7 @@
         <v>102</v>
       </c>
       <c r="AK16" s="24" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AL16" s="13" t="s">
         <v>104</v>
@@ -5260,14 +5233,14 @@
         <v>109</v>
       </c>
       <c r="AR16" s="13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AS16" s="13">
         <v>3</v>
       </c>
-      <c r="AT16" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>16/07/2024</v>
+      <c r="AT16" s="14">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
       </c>
       <c r="AU16" s="11" t="s">
         <v>100</v>
@@ -5275,23 +5248,23 @@
       <c r="AV16" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AW16" s="29" t="s">
+      <c r="AW16" s="28" t="s">
         <v>110</v>
       </c>
       <c r="AX16" s="26" t="s">
         <v>111</v>
       </c>
       <c r="AY16" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="AZ16" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>45489</v>
+        <f t="shared" si="3"/>
+        <v>45503</v>
       </c>
       <c r="BA16" s="14">
-        <f t="shared" ref="BA16" ca="1" si="8">TODAY()+200</f>
-        <v>45789</v>
+        <f t="shared" ref="BA16" si="8">TODAY()+200</f>
+        <v>45803</v>
       </c>
       <c r="BB16" s="27" t="s">
         <v>81</v>
@@ -5299,98 +5272,97 @@
       <c r="BC16" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="BD16" s="28">
-        <v>1930701294397</v>
+      <c r="BD16" s="32">
+        <v>5001101516550</v>
       </c>
       <c r="BE16" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BF16" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG16" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH16" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI16" s="31">
+        <v>912784</v>
+      </c>
+      <c r="BJ16" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BG16" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH16" s="27" t="s">
+      <c r="BK16" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="BI16" s="32">
-        <f ca="1"/>
-        <v>372617</v>
-      </c>
-      <c r="BJ16" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK16" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL16" s="29" t="s">
+      <c r="BL16" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BM16" s="29" t="s">
+      <c r="BM16" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="BN16" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="BO16" s="29" t="s">
+      <c r="BN16" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="BP16" s="29" t="s">
+      <c r="BO16" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="BQ16" s="29" t="s">
+      <c r="BP16" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ16" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="BR16" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS16" s="29" t="s">
+      <c r="BR16" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS16" s="28" t="s">
         <v>100</v>
       </c>
       <c r="BT16" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU16" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="BV16" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW16" s="29" t="s">
+      <c r="BV16" s="28" t="s">
         <v>122</v>
       </c>
+      <c r="BW16" s="28" t="s">
+        <v>123</v>
+      </c>
       <c r="BX16" s="26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BY16" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BZ16" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="CA16" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB16" s="26" t="s">
         <v>81</v>
       </c>
       <c r="CC16" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD16" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="17" spans="4:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.65" customHeight="1" spans="5:32" x14ac:dyDescent="0.25">
       <c r="E17" s="11"/>
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
       <c r="H17" s="13"/>
       <c r="I17" s="13"/>
       <c r="J17" s="13"/>
-      <c r="K17" s="41"/>
-      <c r="L17" s="29"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="28"/>
       <c r="M17" s="26"/>
       <c r="N17" s="26"/>
       <c r="O17" s="26"/>
@@ -5398,10 +5370,10 @@
       <c r="Q17" s="26"/>
       <c r="R17" s="26"/>
       <c r="S17" s="26"/>
-      <c r="T17" s="29"/>
-      <c r="U17" s="31"/>
+      <c r="T17" s="28"/>
+      <c r="U17" s="30"/>
       <c r="V17" s="26"/>
-      <c r="W17" s="41"/>
+      <c r="W17" s="42"/>
       <c r="X17" s="13"/>
       <c r="Y17" s="16"/>
       <c r="AA17" s="20"/>
@@ -5411,7 +5383,7 @@
       <c r="AE17" s="21"/>
       <c r="AF17" s="21"/>
     </row>
-    <row r="18" spans="4:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.65" customHeight="1" spans="27:32" x14ac:dyDescent="0.25">
       <c r="AA18" s="20"/>
       <c r="AB18" s="38"/>
       <c r="AC18" s="20"/>
@@ -5419,7 +5391,7 @@
       <c r="AE18" s="21"/>
       <c r="AF18" s="21"/>
     </row>
-    <row r="19" spans="4:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15.65" customHeight="1" spans="27:32" x14ac:dyDescent="0.25">
       <c r="AA19" s="20"/>
       <c r="AB19" s="36"/>
       <c r="AC19" s="20"/>
@@ -5427,15 +5399,15 @@
       <c r="AE19" s="21"/>
       <c r="AF19" s="21"/>
     </row>
-    <row r="24" spans="4:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D24" s="42"/>
+    <row r="24" ht="15.65" customHeight="1" spans="4:82" x14ac:dyDescent="0.25">
+      <c r="D24" s="43"/>
       <c r="E24" s="11"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
       <c r="H24" s="13"/>
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
-      <c r="K24" s="29"/>
+      <c r="K24" s="28"/>
       <c r="L24" s="11"/>
       <c r="M24" s="13"/>
       <c r="N24" s="13"/>
@@ -5445,9 +5417,9 @@
       <c r="R24" s="13"/>
       <c r="S24" s="13"/>
       <c r="T24" s="16"/>
-      <c r="U24" s="43"/>
+      <c r="U24" s="44"/>
       <c r="V24" s="13"/>
-      <c r="W24" s="41"/>
+      <c r="W24" s="42"/>
       <c r="X24" s="13"/>
       <c r="Y24" s="16"/>
       <c r="Z24" s="16"/>
@@ -5456,12 +5428,12 @@
       <c r="AC24" s="11"/>
       <c r="AD24" s="11"/>
       <c r="AE24" s="11"/>
-      <c r="AF24" s="32"/>
+      <c r="AF24" s="31"/>
       <c r="AG24" s="11"/>
       <c r="AH24" s="14"/>
       <c r="AI24" s="13"/>
-      <c r="AJ24" s="32"/>
-      <c r="AK24" s="32"/>
+      <c r="AJ24" s="31"/>
+      <c r="AK24" s="31"/>
       <c r="AL24" s="13"/>
       <c r="AM24" s="13"/>
       <c r="AN24" s="11"/>
@@ -5473,19 +5445,19 @@
       <c r="AT24" s="16"/>
       <c r="AU24" s="11"/>
       <c r="AV24" s="13"/>
-      <c r="AW24" s="32"/>
+      <c r="AW24" s="31"/>
       <c r="AX24" s="13"/>
-      <c r="AY24" s="29"/>
-      <c r="AZ24" s="29"/>
-      <c r="BA24" s="41"/>
+      <c r="AY24" s="28"/>
+      <c r="AZ24" s="28"/>
+      <c r="BA24" s="42"/>
       <c r="BB24" s="27"/>
       <c r="BC24" s="27"/>
-      <c r="BD24" s="44"/>
+      <c r="BD24" s="45"/>
       <c r="BE24" s="16"/>
       <c r="BF24" s="16"/>
       <c r="BG24" s="27"/>
       <c r="BH24" s="27"/>
-      <c r="BI24" s="32"/>
+      <c r="BI24" s="31"/>
       <c r="BJ24" s="16"/>
       <c r="BK24" s="16"/>
       <c r="BL24" s="11"/>
@@ -5495,7 +5467,7 @@
       <c r="BP24" s="16"/>
       <c r="BQ24" s="27"/>
       <c r="BR24" s="11"/>
-      <c r="BS24" s="45"/>
+      <c r="BS24" s="46"/>
       <c r="BT24" s="27"/>
       <c r="BU24" s="27"/>
       <c r="BV24" s="11"/>
@@ -5508,15 +5480,15 @@
       <c r="CC24" s="27"/>
       <c r="CD24" s="27"/>
     </row>
-    <row r="25" spans="4:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D25" s="42"/>
+    <row r="25" ht="15.65" customHeight="1" spans="4:82" x14ac:dyDescent="0.25">
+      <c r="D25" s="43"/>
       <c r="E25" s="11"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
       <c r="H25" s="13"/>
       <c r="I25" s="13"/>
       <c r="J25" s="13"/>
-      <c r="K25" s="29"/>
+      <c r="K25" s="28"/>
       <c r="L25" s="11"/>
       <c r="M25" s="13"/>
       <c r="N25" s="13"/>
@@ -5526,9 +5498,9 @@
       <c r="R25" s="13"/>
       <c r="S25" s="13"/>
       <c r="T25" s="16"/>
-      <c r="U25" s="43"/>
+      <c r="U25" s="44"/>
       <c r="V25" s="13"/>
-      <c r="W25" s="41"/>
+      <c r="W25" s="42"/>
       <c r="X25" s="13"/>
       <c r="Y25" s="16"/>
       <c r="Z25" s="16"/>
@@ -5537,12 +5509,12 @@
       <c r="AC25" s="11"/>
       <c r="AD25" s="11"/>
       <c r="AE25" s="11"/>
-      <c r="AF25" s="32"/>
+      <c r="AF25" s="31"/>
       <c r="AG25" s="11"/>
       <c r="AH25" s="14"/>
       <c r="AI25" s="13"/>
-      <c r="AJ25" s="32"/>
-      <c r="AK25" s="32"/>
+      <c r="AJ25" s="31"/>
+      <c r="AK25" s="31"/>
       <c r="AL25" s="13"/>
       <c r="AM25" s="13"/>
       <c r="AN25" s="11"/>
@@ -5556,17 +5528,17 @@
       <c r="AV25" s="13"/>
       <c r="AW25" s="11"/>
       <c r="AX25" s="13"/>
-      <c r="AY25" s="29"/>
-      <c r="AZ25" s="29"/>
-      <c r="BA25" s="41"/>
+      <c r="AY25" s="28"/>
+      <c r="AZ25" s="28"/>
+      <c r="BA25" s="42"/>
       <c r="BB25" s="27"/>
       <c r="BC25" s="27"/>
-      <c r="BD25" s="44"/>
+      <c r="BD25" s="45"/>
       <c r="BE25" s="16"/>
       <c r="BF25" s="16"/>
       <c r="BG25" s="27"/>
       <c r="BH25" s="27"/>
-      <c r="BI25" s="32"/>
+      <c r="BI25" s="31"/>
       <c r="BJ25" s="16"/>
       <c r="BK25" s="16"/>
       <c r="BL25" s="11"/>
@@ -5576,7 +5548,7 @@
       <c r="BP25" s="16"/>
       <c r="BQ25" s="27"/>
       <c r="BR25" s="11"/>
-      <c r="BS25" s="45"/>
+      <c r="BS25" s="46"/>
       <c r="BT25" s="27"/>
       <c r="BU25" s="27"/>
       <c r="BV25" s="11"/>
@@ -5589,15 +5561,15 @@
       <c r="CC25" s="27"/>
       <c r="CD25" s="27"/>
     </row>
-    <row r="26" spans="4:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D26" s="42"/>
+    <row r="26" ht="15.65" customHeight="1" spans="4:82" x14ac:dyDescent="0.25">
+      <c r="D26" s="43"/>
       <c r="E26" s="11"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
       <c r="H26" s="13"/>
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
-      <c r="K26" s="29"/>
+      <c r="K26" s="28"/>
       <c r="L26" s="11"/>
       <c r="M26" s="13"/>
       <c r="N26" s="13"/>
@@ -5607,9 +5579,9 @@
       <c r="R26" s="13"/>
       <c r="S26" s="13"/>
       <c r="T26" s="16"/>
-      <c r="U26" s="43"/>
+      <c r="U26" s="44"/>
       <c r="V26" s="13"/>
-      <c r="W26" s="41"/>
+      <c r="W26" s="42"/>
       <c r="X26" s="13"/>
       <c r="Y26" s="16"/>
       <c r="Z26" s="16"/>
@@ -5618,12 +5590,12 @@
       <c r="AC26" s="11"/>
       <c r="AD26" s="11"/>
       <c r="AE26" s="11"/>
-      <c r="AF26" s="32"/>
+      <c r="AF26" s="31"/>
       <c r="AG26" s="11"/>
       <c r="AH26" s="14"/>
       <c r="AI26" s="13"/>
-      <c r="AJ26" s="32"/>
-      <c r="AK26" s="32"/>
+      <c r="AJ26" s="31"/>
+      <c r="AK26" s="31"/>
       <c r="AL26" s="13"/>
       <c r="AM26" s="13"/>
       <c r="AN26" s="11"/>
@@ -5637,17 +5609,17 @@
       <c r="AV26" s="13"/>
       <c r="AW26" s="11"/>
       <c r="AX26" s="13"/>
-      <c r="AY26" s="29"/>
-      <c r="AZ26" s="29"/>
-      <c r="BA26" s="41"/>
+      <c r="AY26" s="28"/>
+      <c r="AZ26" s="28"/>
+      <c r="BA26" s="42"/>
       <c r="BB26" s="27"/>
       <c r="BC26" s="27"/>
-      <c r="BD26" s="44"/>
+      <c r="BD26" s="45"/>
       <c r="BE26" s="16"/>
       <c r="BF26" s="16"/>
       <c r="BG26" s="27"/>
       <c r="BH26" s="27"/>
-      <c r="BI26" s="32"/>
+      <c r="BI26" s="31"/>
       <c r="BJ26" s="16"/>
       <c r="BK26" s="16"/>
       <c r="BL26" s="11"/>
@@ -5657,7 +5629,7 @@
       <c r="BP26" s="16"/>
       <c r="BQ26" s="27"/>
       <c r="BR26" s="11"/>
-      <c r="BS26" s="45"/>
+      <c r="BS26" s="46"/>
       <c r="BT26" s="27"/>
       <c r="BU26" s="27"/>
       <c r="BV26" s="11"/>
@@ -5670,15 +5642,15 @@
       <c r="CC26" s="27"/>
       <c r="CD26" s="27"/>
     </row>
-    <row r="27" spans="4:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D27" s="42"/>
+    <row r="27" ht="15.65" customHeight="1" spans="4:82" x14ac:dyDescent="0.25">
+      <c r="D27" s="43"/>
       <c r="E27" s="11"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
       <c r="H27" s="13"/>
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
-      <c r="K27" s="29"/>
+      <c r="K27" s="28"/>
       <c r="L27" s="11"/>
       <c r="M27" s="13"/>
       <c r="N27" s="13"/>
@@ -5688,9 +5660,9 @@
       <c r="R27" s="13"/>
       <c r="S27" s="13"/>
       <c r="T27" s="16"/>
-      <c r="U27" s="43"/>
+      <c r="U27" s="44"/>
       <c r="V27" s="13"/>
-      <c r="W27" s="41"/>
+      <c r="W27" s="42"/>
       <c r="X27" s="13"/>
       <c r="Y27" s="16"/>
       <c r="Z27" s="16"/>
@@ -5699,12 +5671,12 @@
       <c r="AC27" s="11"/>
       <c r="AD27" s="11"/>
       <c r="AE27" s="11"/>
-      <c r="AF27" s="46"/>
+      <c r="AF27" s="47"/>
       <c r="AG27" s="11"/>
       <c r="AH27" s="14"/>
       <c r="AI27" s="13"/>
-      <c r="AJ27" s="32"/>
-      <c r="AK27" s="32"/>
+      <c r="AJ27" s="31"/>
+      <c r="AK27" s="31"/>
       <c r="AL27" s="13"/>
       <c r="AM27" s="13"/>
       <c r="AN27" s="11"/>
@@ -5717,17 +5689,17 @@
       <c r="AU27" s="11"/>
       <c r="AV27" s="13"/>
       <c r="AX27" s="13"/>
-      <c r="AY27" s="29"/>
-      <c r="AZ27" s="29"/>
-      <c r="BA27" s="41"/>
+      <c r="AY27" s="28"/>
+      <c r="AZ27" s="28"/>
+      <c r="BA27" s="42"/>
       <c r="BB27" s="27"/>
       <c r="BC27" s="27"/>
-      <c r="BD27" s="44"/>
+      <c r="BD27" s="45"/>
       <c r="BE27" s="16"/>
       <c r="BF27" s="16"/>
       <c r="BG27" s="27"/>
       <c r="BH27" s="27"/>
-      <c r="BI27" s="32"/>
+      <c r="BI27" s="31"/>
       <c r="BJ27" s="16"/>
       <c r="BK27" s="16"/>
       <c r="BL27" s="11"/>
@@ -5737,7 +5709,7 @@
       <c r="BP27" s="16"/>
       <c r="BQ27" s="27"/>
       <c r="BR27" s="11"/>
-      <c r="BS27" s="45"/>
+      <c r="BS27" s="46"/>
       <c r="BT27" s="27"/>
       <c r="BU27" s="27"/>
       <c r="BV27" s="11"/>
@@ -5750,15 +5722,15 @@
       <c r="CC27" s="27"/>
       <c r="CD27" s="27"/>
     </row>
-    <row r="28" spans="4:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D28" s="42"/>
+    <row r="28" ht="15.65" customHeight="1" spans="4:82" x14ac:dyDescent="0.25">
+      <c r="D28" s="43"/>
       <c r="E28" s="11"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
-      <c r="K28" s="29"/>
+      <c r="K28" s="28"/>
       <c r="L28" s="11"/>
       <c r="M28" s="13"/>
       <c r="N28" s="13"/>
@@ -5768,9 +5740,9 @@
       <c r="R28" s="13"/>
       <c r="S28" s="13"/>
       <c r="T28" s="16"/>
-      <c r="U28" s="43"/>
+      <c r="U28" s="44"/>
       <c r="V28" s="13"/>
-      <c r="W28" s="41"/>
+      <c r="W28" s="42"/>
       <c r="X28" s="13"/>
       <c r="Y28" s="16"/>
       <c r="Z28" s="16"/>
@@ -5779,12 +5751,12 @@
       <c r="AC28" s="11"/>
       <c r="AD28" s="11"/>
       <c r="AE28" s="11"/>
-      <c r="AF28" s="46"/>
+      <c r="AF28" s="47"/>
       <c r="AG28" s="11"/>
       <c r="AH28" s="14"/>
       <c r="AI28" s="13"/>
-      <c r="AJ28" s="32"/>
-      <c r="AK28" s="32"/>
+      <c r="AJ28" s="31"/>
+      <c r="AK28" s="31"/>
       <c r="AL28" s="13"/>
       <c r="AM28" s="13"/>
       <c r="AN28" s="11"/>
@@ -5798,17 +5770,17 @@
       <c r="AV28" s="13"/>
       <c r="AW28" s="11"/>
       <c r="AX28" s="13"/>
-      <c r="AY28" s="29"/>
-      <c r="AZ28" s="29"/>
-      <c r="BA28" s="41"/>
+      <c r="AY28" s="28"/>
+      <c r="AZ28" s="28"/>
+      <c r="BA28" s="42"/>
       <c r="BB28" s="27"/>
       <c r="BC28" s="27"/>
-      <c r="BD28" s="44"/>
+      <c r="BD28" s="45"/>
       <c r="BE28" s="16"/>
       <c r="BF28" s="16"/>
       <c r="BG28" s="27"/>
       <c r="BH28" s="27"/>
-      <c r="BI28" s="32"/>
+      <c r="BI28" s="31"/>
       <c r="BJ28" s="16"/>
       <c r="BK28" s="16"/>
       <c r="BL28" s="11"/>
@@ -5818,7 +5790,7 @@
       <c r="BP28" s="16"/>
       <c r="BQ28" s="27"/>
       <c r="BR28" s="11"/>
-      <c r="BS28" s="45"/>
+      <c r="BS28" s="46"/>
       <c r="BT28" s="27"/>
       <c r="BU28" s="27"/>
       <c r="BV28" s="11"/>
@@ -5831,15 +5803,15 @@
       <c r="CC28" s="27"/>
       <c r="CD28" s="27"/>
     </row>
-    <row r="29" spans="4:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D29" s="42"/>
+    <row r="29" ht="15.65" customHeight="1" spans="4:82" x14ac:dyDescent="0.25">
+      <c r="D29" s="43"/>
       <c r="E29" s="11"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="40"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
       <c r="H29" s="13"/>
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
-      <c r="K29" s="29"/>
+      <c r="K29" s="28"/>
       <c r="L29" s="11"/>
       <c r="M29" s="13"/>
       <c r="N29" s="13"/>
@@ -5849,9 +5821,9 @@
       <c r="R29" s="13"/>
       <c r="S29" s="13"/>
       <c r="T29" s="16"/>
-      <c r="U29" s="43"/>
+      <c r="U29" s="44"/>
       <c r="V29" s="13"/>
-      <c r="W29" s="41"/>
+      <c r="W29" s="42"/>
       <c r="X29" s="13"/>
       <c r="Y29" s="16"/>
       <c r="Z29" s="16"/>
@@ -5860,12 +5832,12 @@
       <c r="AC29" s="11"/>
       <c r="AD29" s="11"/>
       <c r="AE29" s="11"/>
-      <c r="AF29" s="32"/>
+      <c r="AF29" s="31"/>
       <c r="AG29" s="11"/>
       <c r="AH29" s="14"/>
       <c r="AI29" s="13"/>
-      <c r="AJ29" s="32"/>
-      <c r="AK29" s="32"/>
+      <c r="AJ29" s="31"/>
+      <c r="AK29" s="31"/>
       <c r="AL29" s="13"/>
       <c r="AM29" s="13"/>
       <c r="AN29" s="11"/>
@@ -5877,19 +5849,19 @@
       <c r="AT29" s="16"/>
       <c r="AU29" s="11"/>
       <c r="AV29" s="13"/>
-      <c r="AW29" s="32"/>
+      <c r="AW29" s="31"/>
       <c r="AX29" s="13"/>
-      <c r="AY29" s="29"/>
-      <c r="AZ29" s="29"/>
-      <c r="BA29" s="41"/>
+      <c r="AY29" s="28"/>
+      <c r="AZ29" s="28"/>
+      <c r="BA29" s="42"/>
       <c r="BB29" s="27"/>
       <c r="BC29" s="27"/>
-      <c r="BD29" s="44"/>
+      <c r="BD29" s="45"/>
       <c r="BE29" s="16"/>
       <c r="BF29" s="16"/>
       <c r="BG29" s="27"/>
       <c r="BH29" s="27"/>
-      <c r="BI29" s="32"/>
+      <c r="BI29" s="31"/>
       <c r="BJ29" s="16"/>
       <c r="BK29" s="16"/>
       <c r="BL29" s="11"/>
@@ -5899,7 +5871,7 @@
       <c r="BP29" s="16"/>
       <c r="BQ29" s="27"/>
       <c r="BR29" s="11"/>
-      <c r="BS29" s="45"/>
+      <c r="BS29" s="46"/>
       <c r="BT29" s="27"/>
       <c r="BU29" s="27"/>
       <c r="BV29" s="11"/>
@@ -5912,15 +5884,15 @@
       <c r="CC29" s="27"/>
       <c r="CD29" s="27"/>
     </row>
-    <row r="30" spans="4:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D30" s="42"/>
+    <row r="30" ht="15.65" customHeight="1" spans="4:82" x14ac:dyDescent="0.25">
+      <c r="D30" s="43"/>
       <c r="E30" s="11"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
-      <c r="K30" s="29"/>
+      <c r="K30" s="28"/>
       <c r="L30" s="11"/>
       <c r="M30" s="13"/>
       <c r="N30" s="13"/>
@@ -5930,9 +5902,9 @@
       <c r="R30" s="13"/>
       <c r="S30" s="13"/>
       <c r="T30" s="16"/>
-      <c r="U30" s="43"/>
+      <c r="U30" s="44"/>
       <c r="V30" s="13"/>
-      <c r="W30" s="41"/>
+      <c r="W30" s="42"/>
       <c r="X30" s="13"/>
       <c r="Y30" s="16"/>
       <c r="Z30" s="16"/>
@@ -5941,12 +5913,12 @@
       <c r="AC30" s="11"/>
       <c r="AD30" s="11"/>
       <c r="AE30" s="11"/>
-      <c r="AF30" s="32"/>
+      <c r="AF30" s="31"/>
       <c r="AG30" s="11"/>
       <c r="AH30" s="14"/>
       <c r="AI30" s="13"/>
-      <c r="AJ30" s="32"/>
-      <c r="AK30" s="32"/>
+      <c r="AJ30" s="31"/>
+      <c r="AK30" s="31"/>
       <c r="AL30" s="13"/>
       <c r="AM30" s="13"/>
       <c r="AN30" s="11"/>
@@ -5960,17 +5932,17 @@
       <c r="AV30" s="13"/>
       <c r="AW30" s="11"/>
       <c r="AX30" s="13"/>
-      <c r="AY30" s="29"/>
-      <c r="AZ30" s="29"/>
-      <c r="BA30" s="41"/>
+      <c r="AY30" s="28"/>
+      <c r="AZ30" s="28"/>
+      <c r="BA30" s="42"/>
       <c r="BB30" s="27"/>
       <c r="BC30" s="27"/>
-      <c r="BD30" s="44"/>
+      <c r="BD30" s="45"/>
       <c r="BE30" s="16"/>
       <c r="BF30" s="16"/>
       <c r="BG30" s="27"/>
       <c r="BH30" s="27"/>
-      <c r="BI30" s="32"/>
+      <c r="BI30" s="31"/>
       <c r="BJ30" s="16"/>
       <c r="BK30" s="16"/>
       <c r="BL30" s="11"/>
@@ -5980,7 +5952,7 @@
       <c r="BP30" s="16"/>
       <c r="BQ30" s="27"/>
       <c r="BR30" s="11"/>
-      <c r="BS30" s="45"/>
+      <c r="BS30" s="46"/>
       <c r="BT30" s="27"/>
       <c r="BU30" s="27"/>
       <c r="BV30" s="11"/>
@@ -5993,15 +5965,15 @@
       <c r="CC30" s="27"/>
       <c r="CD30" s="27"/>
     </row>
-    <row r="32" spans="4:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D32" s="42"/>
+    <row r="32" ht="15.65" customHeight="1" spans="4:82" x14ac:dyDescent="0.25">
+      <c r="D32" s="43"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="40"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
       <c r="H32" s="13"/>
       <c r="I32" s="13"/>
       <c r="J32" s="13"/>
-      <c r="K32" s="29"/>
+      <c r="K32" s="28"/>
       <c r="L32" s="11"/>
       <c r="M32" s="13"/>
       <c r="N32" s="13"/>
@@ -6011,9 +5983,9 @@
       <c r="R32" s="13"/>
       <c r="S32" s="13"/>
       <c r="T32" s="16"/>
-      <c r="U32" s="43"/>
+      <c r="U32" s="44"/>
       <c r="V32" s="13"/>
-      <c r="W32" s="41"/>
+      <c r="W32" s="42"/>
       <c r="X32" s="13"/>
       <c r="Y32" s="16"/>
       <c r="Z32" s="16"/>
@@ -6022,12 +5994,12 @@
       <c r="AC32" s="11"/>
       <c r="AD32" s="11"/>
       <c r="AE32" s="11"/>
-      <c r="AF32" s="32"/>
+      <c r="AF32" s="31"/>
       <c r="AG32" s="11"/>
       <c r="AH32" s="14"/>
       <c r="AI32" s="13"/>
-      <c r="AJ32" s="32"/>
-      <c r="AK32" s="32"/>
+      <c r="AJ32" s="31"/>
+      <c r="AK32" s="31"/>
       <c r="AL32" s="13"/>
       <c r="AM32" s="13"/>
       <c r="AN32" s="11"/>
@@ -6041,17 +6013,17 @@
       <c r="AV32" s="13"/>
       <c r="AW32" s="11"/>
       <c r="AX32" s="13"/>
-      <c r="AY32" s="29"/>
-      <c r="AZ32" s="29"/>
-      <c r="BA32" s="41"/>
+      <c r="AY32" s="28"/>
+      <c r="AZ32" s="28"/>
+      <c r="BA32" s="42"/>
       <c r="BB32" s="27"/>
       <c r="BC32" s="27"/>
-      <c r="BD32" s="44"/>
+      <c r="BD32" s="45"/>
       <c r="BE32" s="16"/>
       <c r="BF32" s="16"/>
       <c r="BG32" s="27"/>
       <c r="BH32" s="27"/>
-      <c r="BI32" s="32"/>
+      <c r="BI32" s="31"/>
       <c r="BJ32" s="16"/>
       <c r="BK32" s="16"/>
       <c r="BL32" s="11"/>
@@ -6061,7 +6033,7 @@
       <c r="BP32" s="16"/>
       <c r="BQ32" s="27"/>
       <c r="BR32" s="11"/>
-      <c r="BS32" s="45"/>
+      <c r="BS32" s="46"/>
       <c r="BT32" s="27"/>
       <c r="BU32" s="27"/>
       <c r="BV32" s="11"/>
@@ -6075,75 +6047,225 @@
       <c r="CD32" s="27"/>
     </row>
   </sheetData>
-  <dataValidations count="16">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX10:AX16 X10:X17 V10:V17 S10:S17 BX10:BX16" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="66">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX10:AX16">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX16 X2:X17 V2:V17 S2:S17 BX2:BX16" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX16">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX24 X24 V24 S24 BX24" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX24">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX25:AX26 X32 X30 X25:X26 V32 V30 V25:V26 S32 S30 S25:S26 J8 J6 J4 J30 J2 J16 J14 J12 J10 I9 I7 I5 I32:J32 I3 I27:I30 I24:J25 I17 I15 I13 I11 BX32 BX30 BX25:BX26 AX32 AX30" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX25:AX26">
       <formula1>INDIRECT(#REF!)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX27:AX29 X27:X29 V27:V29 S27:S29 BX27:BX29" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX27:AX29">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J11" xr:uid="{00000000-0002-0000-0000-00001A000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX30">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX32">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BX10:BX16">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J13" xr:uid="{00000000-0002-0000-0000-00001C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BX2:BX16">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J15" xr:uid="{00000000-0002-0000-0000-00001E000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BX24">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J17" xr:uid="{00000000-0002-0000-0000-000020000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BX25:BX26">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BX27:BX29">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J26" xr:uid="{00000000-0002-0000-0000-000022000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BX30">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BX32">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I11">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I13">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I15">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I17">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I24:J25">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I27:I30">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I32:J32">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I7">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I9">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J11">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J12">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J13">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J14">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J15">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J16">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J17">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J26">
       <formula1>INDIRECT($E6)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J27" xr:uid="{00000000-0002-0000-0000-000023000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J27">
       <formula1>INDIRECT($E3)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J28:J29" xr:uid="{00000000-0002-0000-0000-000024000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J28:J29">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3" xr:uid="{00000000-0002-0000-0000-000025000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J5" xr:uid="{00000000-0002-0000-0000-000028000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J30">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J5">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J7" xr:uid="{00000000-0002-0000-0000-00002A000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J6">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J7">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J9" xr:uid="{00000000-0002-0000-0000-00002C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J8">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J9">
       <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S10:S17">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S17">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S24">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S25:S26">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S27:S29">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S30">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S32">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V10:V17">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V17">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V24">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V25:V26">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V27:V29">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V30">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V32">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X10:X17">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X17">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X24">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X25:X26">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X27:X29">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X30">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X32">
+      <formula1>INDIRECT(#REF!)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="U3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="U4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="U5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="U6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="U7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="U8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="U9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="U10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="U11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="U12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="U13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="U14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="U15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="U16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="U2" r:id="rId1"/>
+    <hyperlink ref="U3" r:id="rId2"/>
+    <hyperlink ref="U4" r:id="rId3"/>
+    <hyperlink ref="U5" r:id="rId4"/>
+    <hyperlink ref="U6" r:id="rId5"/>
+    <hyperlink ref="U7" r:id="rId6"/>
+    <hyperlink ref="U8" r:id="rId7"/>
+    <hyperlink ref="U9" r:id="rId8"/>
+    <hyperlink ref="U10" r:id="rId9"/>
+    <hyperlink ref="U11" r:id="rId10"/>
+    <hyperlink ref="U12" r:id="rId11"/>
+    <hyperlink ref="U13" r:id="rId12"/>
+    <hyperlink ref="U14" r:id="rId13"/>
+    <hyperlink ref="U15" r:id="rId14"/>
+    <hyperlink ref="U16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>
